--- a/data/trans_dic/IP12B$oido-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,85</t>
+          <t>0,0; 39,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,43</t>
+          <t>0,0; 41,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,62</t>
+          <t>0,0; 30,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 54,78</t>
+          <t>6,94; 55,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,9</t>
+          <t>0,0; 47,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 37,42</t>
+          <t>4,16; 36,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,54</t>
+          <t>0,0; 28,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,78</t>
+          <t>0,0; 26,85</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,3</t>
+          <t>0,0; 30,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,88</t>
+          <t>0,0; 54,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>0,0; 26,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,28</t>
+          <t>0,0; 22,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,61</t>
+          <t>0,0; 43,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,85</t>
+          <t>0,0; 42,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,83</t>
+          <t>0,0; 24,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,83</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,06</t>
+          <t>0,0; 23,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,84</t>
+          <t>0,0; 13,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,18</t>
+          <t>0,0; 23,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,49</t>
+          <t>0,0; 18,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,33</t>
+          <t>1,8; 16,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,23</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,79</t>
+          <t>0,0; 38,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,7</t>
+          <t>0,0; 36,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,11</t>
+          <t>0,0; 33,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,73</t>
+          <t>0,0; 41,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 27,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,09</t>
+          <t>0,0; 23,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,53</t>
+          <t>0,0; 24,38</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,85</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,86</t>
+          <t>0,0; 81,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,05</t>
+          <t>0,0; 54,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,2</t>
+          <t>0,0; 70,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,2</t>
+          <t>0,0; 45,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 65,66</t>
+          <t>7,46; 59,67</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 13,1</t>
+          <t>1,24; 11,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 15,04</t>
+          <t>3,43; 15,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,46</t>
+          <t>2,15; 13,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,29</t>
+          <t>1,46; 13,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,38</t>
+          <t>2,5; 14,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,14</t>
+          <t>1,25; 12,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,84</t>
+          <t>2,22; 9,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,28</t>
+          <t>4,16; 12,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,39</t>
+          <t>2,49; 10,08</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2544</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2296</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3553</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2978</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>600; 4790</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3127</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>599; 5219</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4411</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3650</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3685</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3328</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3372</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3995</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1880</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3331</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2780</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3487</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4114</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2727</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5296</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3039</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>718; 6522</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3502</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3189</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4426</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3416</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3117</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3859</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5074</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4316</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2905</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2769</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3508</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2754</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4232</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>544; 4351</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4915</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>8773</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>513; 4705</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2080; 9400</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1133; 7038</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>681; 6145</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1467; 8453</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>573; 5513</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1954; 8729</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4966; 15086</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2456; 9954</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$oido-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,92</t>
+          <t>0,0; 47,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,14</t>
+          <t>0,0; 43,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,98</t>
+          <t>0,0; 32,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 55,35</t>
+          <t>6,95; 54,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,29</t>
+          <t>0,0; 46,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 36,23</t>
+          <t>4,76; 37,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,93</t>
+          <t>0,0; 28,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,85</t>
+          <t>0,0; 23,73</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,36</t>
+          <t>0,0; 31,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,93</t>
+          <t>0,0; 49,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,77</t>
+          <t>0,0; 22,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,54</t>
+          <t>0,0; 24,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,1</t>
+          <t>0,0; 41,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,49</t>
+          <t>0,0; 36,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,75</t>
+          <t>0,0; 20,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,66</t>
+          <t>0,0; 23,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,7</t>
+          <t>0,0; 21,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,27</t>
+          <t>0,0; 13,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,43</t>
+          <t>0,0; 25,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,01</t>
+          <t>0,0; 18,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,32</t>
+          <t>1,83; 16,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 10,2</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,77</t>
+          <t>0,0; 44,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,6</t>
+          <t>0,0; 35,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,25</t>
+          <t>0,0; 24,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,94</t>
+          <t>0,0; 44,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,11</t>
+          <t>0,0; 23,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,39</t>
+          <t>0,0; 23,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,38</t>
+          <t>0,0; 24,29</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 79,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,29</t>
+          <t>0,0; 83,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,82</t>
+          <t>0,0; 46,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,87</t>
+          <t>0,0; 67,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,48</t>
+          <t>0,0; 41,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 59,67</t>
+          <t>7,78; 57,45</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,34</t>
+          <t>1,23; 11,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 15,49</t>
+          <t>3,52; 15,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 13,33</t>
+          <t>2,22; 13,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,16</t>
+          <t>1,49; 14,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 14,42</t>
+          <t>2,52; 13,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,0</t>
+          <t>1,23; 11,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,9</t>
+          <t>2,27; 10,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,64</t>
+          <t>4,0; 11,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,08</t>
+          <t>2,49; 9,97</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,27 +1639,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2296</t>
+          <t>0; 2742</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3553</t>
+          <t>0; 3792</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2978</t>
+          <t>0; 3094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>600; 4790</t>
+          <t>601; 4714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3127</t>
+          <t>0; 3085</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>599; 5219</t>
+          <t>685; 5438</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4411</t>
+          <t>0; 4310</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3650</t>
+          <t>0; 3225</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3685</t>
+          <t>0; 3792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3328</t>
+          <t>0; 2975</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3372</t>
+          <t>0; 2811</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3995</t>
+          <t>0; 4257</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1880</t>
+          <t>0; 1823</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3331</t>
+          <t>0; 2877</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2780</t>
+          <t>0; 2262</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3487</t>
+          <t>0; 3595</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4114</t>
+          <t>0; 3653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2727</t>
+          <t>0; 2723</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5296</t>
+          <t>0; 5732</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3039</t>
+          <t>0; 3072</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>718; 6522</t>
+          <t>733; 6491</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3502</t>
+          <t>0; 3816</t>
         </is>
       </c>
     </row>
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3189</t>
+          <t>0; 3646</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4426</t>
+          <t>0; 4256</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3416</t>
+          <t>0; 2518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3117</t>
+          <t>0; 3340</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3859</t>
+          <t>0; 3293</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5074</t>
+          <t>0; 5146</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4316</t>
+          <t>0; 4300</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2905</t>
+          <t>0; 2320</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2769</t>
+          <t>0; 2838</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3508</t>
+          <t>0; 2972</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2754</t>
+          <t>0; 2620</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4232</t>
+          <t>0; 3862</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>544; 4351</t>
+          <t>567; 4190</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>513; 4705</t>
+          <t>509; 4793</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2080; 9400</t>
+          <t>2138; 9204</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1133; 7038</t>
+          <t>1171; 7160</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>681; 6145</t>
+          <t>697; 6587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1467; 8453</t>
+          <t>1476; 8156</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>573; 5513</t>
+          <t>563; 5287</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1954; 8729</t>
+          <t>1998; 9180</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4966; 15086</t>
+          <t>4769; 14305</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2456; 9954</t>
+          <t>2460; 9840</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$oido-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,04%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,27%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,67</t>
+          <t>6,95; 54,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,91</t>
+          <t>0,0; 46,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 54,48</t>
+          <t>0,0; 38,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,65</t>
+          <t>0,0; 39,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 31,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 37,74</t>
+          <t>4,86; 37,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,27</t>
+          <t>0,0; 31,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,73</t>
+          <t>0,0; 30,78</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,37%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 49,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,31</t>
+          <t>0,0; 22,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,02</t>
+          <t>0,0; 25,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12,07%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,15</t>
+          <t>0,0; 20,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,36</t>
+          <t>0,0; 22,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,04</t>
+          <t>0,0; 25,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,25</t>
+          <t>0,0; 16,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,36</t>
+          <t>0,0; 21,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,2</t>
+          <t>0,0; 15,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,24</t>
+          <t>1,79; 15,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,2</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,75%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>11,94%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,81%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,51</t>
+          <t>0,0; 49,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 35,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,94</t>
+          <t>0,0; 31,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,13</t>
+          <t>0,0; 26,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,72</t>
+          <t>0,0; 23,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,29</t>
+          <t>0,0; 25,53</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26,46%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>39,19%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,27 +1233,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 46,05</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 67,2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 79,85</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 83,32</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 46,44</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,42</t>
+          <t>0,0; 83,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,51</t>
+          <t>0,0; 42,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,78; 57,45</t>
+          <t>7,91; 65,66</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,26%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8,1%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,03%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,56</t>
+          <t>1,46; 12,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,17</t>
+          <t>2,48; 14,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,56</t>
+          <t>1,23; 12,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,1</t>
+          <t>1,24; 13,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 13,91</t>
+          <t>3,5; 15,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,51</t>
+          <t>2,21; 13,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,41</t>
+          <t>2,18; 9,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,99</t>
+          <t>4,21; 12,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,97</t>
+          <t>2,51; 9,39</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>714</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>715</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2742</t>
+          <t>601; 4741</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3792</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3094</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>601; 4714</t>
+          <t>0; 2235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3085</t>
+          <t>0; 3405</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3039</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>685; 5438</t>
+          <t>700; 5392</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4310</t>
+          <t>0; 4810</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 4183</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1749,27 +1749,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1259</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3022</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3792</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2811</t>
+          <t>0; 2889</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4257</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1859,14 +1859,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1912,27 +1912,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1823</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2262</t>
+          <t>0; 2339</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3595</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2027,22 +2027,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2080,27 +2080,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3653</t>
+          <t>0; 5689</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2723</t>
+          <t>0; 2782</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3072</t>
+          <t>0; 3256</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>733; 6491</t>
+          <t>714; 6128</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3816</t>
+          <t>0; 3454</t>
         </is>
       </c>
     </row>
@@ -2185,27 +2185,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1444</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>597</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3646</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4256</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2518</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4317</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3340</t>
+          <t>0; 3195</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>0; 3715</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5146</t>
+          <t>0; 5009</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4300</t>
+          <t>0; 4521</t>
         </is>
       </c>
     </row>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2406,27 +2406,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>769</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1335</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2459,27 +2459,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>0; 2947</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2611</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2320</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2838</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2972</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2620</t>
+          <t>0; 2856</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3862</t>
+          <t>0; 3926</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>567; 4190</t>
+          <t>577; 4788</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1767</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>4915</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3183</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3857</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>509; 4793</t>
+          <t>682; 5742</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2138; 9204</t>
+          <t>1454; 8432</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1171; 7160</t>
+          <t>565; 5576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>697; 6587</t>
+          <t>512; 5434</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1476; 8156</t>
+          <t>2124; 9129</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>563; 5287</t>
+          <t>1165; 7106</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1998; 9180</t>
+          <t>1925; 8680</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4769; 14305</t>
+          <t>5020; 14649</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2460; 9840</t>
+          <t>2474; 9276</t>
         </is>
       </c>
     </row>
